--- a/docs/이랜드건설_승진기준.xlsx
+++ b/docs/이랜드건설_승진기준.xlsx
@@ -2033,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>사원에서 주임으로 승진하려면 어떤 조건을 충족해야 하나요?</t>
+          <t>사원에서 주임으로 승진하려면 최소 몇 년을 근무해야 하나요?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>사원에서 주임으로 승진하기 위해서는 ①최소 2년 이상 재직해야 하고, ②연간 목표 달성률(KPI) 70% 이상, ③프로젝트 기여도 보통 이상, ④직무 전문성 기본 이상, ⑤커뮤니케이션·협업 보통 이상, ⑥동료평가 60점 이상, ⑦필수 교육 100% 이수, ⑧사내외 교육 20시간 이수, ⑨최근 1년간 징계 이력이 없어야 합니다.</t>
+          <t>최소 2년 이상 재직해야 하며, 그 외에 업적 평가(KPI 70% 이상), 역량 평가, 동료평가(60점 이상), 필수 교육 이수(100%), 지난 1년간 징계 이력이 없어야 합니다.</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KPI(연간 목표 달성률)가 승진에 미치는 영향은 얼마나 되나요?</t>
+          <t>승진 심사에서 가장 큰 비중을 차지하는 평가 항목은 무엇인가요?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KPI는 업적 평가에서 가장 큰 비중(35%)을 차지하는 평가항목입니다. 직급이 올라갈수록 요구되는 기준이 높아져서 사원→주임 70% 이상, 주임→대리 75% 이상, 대리→과장 80% 이상, 과장→차장 85% 이상, 차장→부장 90% 이상을 달성해야 합니다. 상·하반기 합산으로 평가됩니다.</t>
+          <t>업적 평가가 가장 큰 비중을 차지하며, 연간 목표 달성률(KPI)이 35%, 프로젝트 기여도 15%, 원가절감 기여실적 5%로 총 55%입니다.</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>동료평가 점수는 어떻게 활용되나요?</t>
+          <t>대리에서 과장으로 승진할 때 동료평가 점수는 몇 점 이상이어야 하나요?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>동료평가는 전사 직원들의 피어피드백을 구글폼으로 수집하며, 다면평가의 10%를 차지합니다. 직급별로 요구되는 점수가 다른데, 사원 60점, 주임 65점, 대리 70점, 과장 75점, 차장 80점 이상이 필요합니다. 특히 대리 이상 직급에서는 동료평가가 정식으로 반영됩니다.</t>
+          <t>동료평가 점수는 70점 이상이어야 합니다. 또한 최소 3년 이상 대리직급을 유지해야 하고, KPI 80% 이상 달성, 고급 이상의 직무 전문성, 팀 코칭 경험, 2인 이상의 팀장급 추천서가 필요합니다.</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>탁월한 성과를 낸 경우 재직기간을 단축할 수 있나요?</t>
+          <t>뛰어난 성과를 낸 경우 승진 요건을 단축받을 수 있나요?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>네, 가능합니다. 각 직급에서 탁월한 성과를 낸 직원은 일반적으로 요구되는 직급별 체류연수를 1년 단축할 수 있습니다. 다만 최소 재직기간 요건은 예외 승인 절차를 거쳐야 합니다.</t>
+          <t>네, 탁월한 성과를 낸 직원은 각 직급별 체류연수를 1년 단축받을 수 있습니다. 다만 인사위원회의 예외 승인이 필요합니다.</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>대리 이상에서 요구되는 리더십 평가 기준은 무엇인가요?</t>
+          <t>과장에서 차장으로 승진하기 위해 원가절감 기여는 몇 건 이상 필요한가요?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>리더십 및 조직관리 평가는 대리 이상부터 적용되며, 가중치는 10%입니다. 대리는 팀원 코칭 능력, 과장은 팀 운영 능력, 차장 이상은 조직 운영 능력이 요구됩니다. 또한 대리부터 부장까지 직급별로 1명 이상의 후배 멘토링이 필수입니다.</t>
+          <t>과장에서 차장 승진 시 원가절감 기여실적은 3건 이상이어야 합니다.</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>원가절감 기여는 어느 직급부터 승진에 필요한가요?</t>
+          <t>징계 이력이 있으면 승진이 불가능한가요?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>원가절감 기여도는 대리 이상부터 승진 평가에 반영됩니다(가중치 5%). 구체적으로는 대리 1건, 과장 3건, 차장 5건 이상의 원가절감 실적이 필요하며, 금액 기준으로 별도 산정됩니다.</t>
+          <t>감봉 이상의 징계를 받은 경우 승진이 제한됩니다. 직급에 따라 1년(사원→주임, 주임→대리)에서 3년(차장→부장) 동안 징계 이력이 없어야 합니다.</t>
         </is>
       </c>
     </row>
@@ -2170,12 +2170,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>자격증은 몇 개를 보유해야 하나요?</t>
+          <t>중대재해와 관련이 있으면 승진에 어떤 영향을 미치나요?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>자격증 보유 기준은 직급마다 다릅니다. 사원은 요구되지 않으며, 주임부터 1개, 과장부터는 2개 이상의 자격증이 필요합니다. 건설기술인 경력도 자격증으로 인정됩니다.</t>
+          <t>중대재해 연루 시 3년간 모든 직급 승진이 제한됩니다.</t>
         </is>
       </c>
     </row>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>사내외 교육 이수 시간은 얼마나 필요한가요?</t>
+          <t>주임 직급에서 자격증이 필요한가요?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>연간 필요 교육 이수 시간은 직급별로 다릅니다. 사원 20시간, 주임 30시간, 대리 이상은 40시간이 필요합니다. 여기에는 그룹 교육과 법정 필수교육이 포함되며, 100% 이수율을 유지해야 합니다.</t>
+          <t>네, 주임 이상부터 직무 관련 자격증 1개 이상 보유가 필수입니다. 건설기술인 경력도 인정됩니다.</t>
         </is>
       </c>
     </row>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>징계 이력이 있으면 승진이 불가능한가요?</t>
+          <t>대리 이상 직급에서 리더십 평가는 어떻게 이루어지나요?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>네, 리스크 관리 기준으로 감봉 이상의 징계 이력이 있으면 승진이 제한됩니다. 필요한 무징계 기간은 직급별로 다른데, 사원→주임·주임→대리는 1년, 대리→과장·과장→차장은 2년, 차장→부장은 3년 이상 징계 이력이 없어야 합니다.</t>
+          <t>대리 이상부터 리더십 및 조직관리 역량이 평가되며, 대리는 팀원 코칭, 과장은 팀 운영, 차장 이상은 조직 운영 수준이 요구됩니다.</t>
         </is>
       </c>
     </row>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>안전사고나 중대재해와 관련된 승진 제한이 있나요?</t>
+          <t>후배 육성 및 멘토링이 승진에 영향을 미치나요?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>네, 있습니다. 모든 직급에서 안전사고 연루 여부가 심사 대상이며, 특히 중대재해와 연루된 경우 3년간 승진이 제한됩니다. 근로기준법 위반 등 노무 컴플라이언스 위반도 모든 직급에서 승진을 제한하는 사유입니다.</t>
+          <t>네, 후배 육성 및 멘토링은 조직 기여 항목으로 평가됩니다. 대리는 1명, 과장은 2명, 차장 이상은 3명 이상의 공식 멘토링이 필요합니다.</t>
         </is>
       </c>
     </row>
@@ -2238,46 +2238,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>상위 직급자 추천서는 몇 명이 필요한가요?</t>
+          <t>승진 평가는 얼마나 자주 진행되나요?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>승진 시 필요한 추천서 수는 직급별로 다릅니다. 사원→주임, 주임→대리는 팀장급 이상 1인, 대리→과장, 과장→차장은 2인, 차장→부장은 3인의 추천서가 필요합니다.</t>
+          <t>대부분의 평가 항목은 연 2회(상·하반기) 진행되며, 원가절감 기여실적과 신규 사업 개설 기여는 연간 평가됩니다. 근속 요건과 리스크 관리는 상시 모니터링됩니다.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>평가/승진</t>
+          <t>근무</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>신규 사업·현장 개설 기여는 어느 직급부터 필요한가요?</t>
+          <t>건설기술인 경력은 자격증으로 인정되나요?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>신규 사업·현장 개설 기여(수주·계약 기여 포함)는 과장부터 승진 평가에 반영되기 시작합니다. 과장→차장 승진 시 1건, 차장→부장 승진 시 2건 이상의 기여가 필요합니다.</t>
+          <t>네, 직무 관련 자격증 보유 요건에 건설기술인 경력이 포함됩니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>근무</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>법정 필수교육을 이수하지 않으면 승진할 수 없나요?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>네, 모든 직급 승진 시 연간 필수 교육 이수율 100%가 필수 조건입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>평가/승진</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>다면평가의 구성 요소는 무엇인가요?</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>다면평가는 총 10%의 가중치를 차지하며, 동료평가 점수(피어피드백)가 주요 요소입니다. 동료평가는 구글폼 기반으로 수집되며,</t>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차장 이상으로 승진하려면 CEO나 임원 추천이 필수인가요?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>차장 승진부터 CEO·임원 추천이 필요하며, 최소 3년 이상 과장직급 근무와 KPI 85% 이상, 신규 사업 개설 기여 1건 이상이 필수입니다.</t>
         </is>
       </c>
     </row>
